--- a/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
+++ b/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:39:33+00:00</t>
+    <t>2026-09-23T11:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
+++ b/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:46:09+00:00</t>
+    <t>2026-09-23T12:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
+++ b/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:15:24+00:00</t>
+    <t>2026-09-23T12:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
+++ b/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:19:55+00:00</t>
+    <t>2026-09-23T12:32:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
+++ b/feature-th-deidentification/StructureDefinition-santeon-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:32:00+00:00</t>
+    <t>2026-09-23T18:28:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
